--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10817"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD04E798-FF56-C142-B406-874CB0518ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="20160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680"/>
   </bookViews>
   <sheets>
-    <sheet name="products" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="products" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="dashboard" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="134">
   <si>
     <t>id</t>
   </si>
@@ -30,19 +30,406 @@
   </si>
   <si>
     <t>my first prod</t>
+  </si>
+  <si>
+    <t>txid</t>
+  </si>
+  <si>
+    <t>Dashcaption</t>
+  </si>
+  <si>
+    <t>dash_image</t>
+  </si>
+  <si>
+    <t>appviewsheet</t>
+  </si>
+  <si>
+    <t>parentview</t>
+  </si>
+  <si>
+    <t>userrole</t>
+  </si>
+  <si>
+    <t>screen_order</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>dashboard_Images/80486473.image.090130.png</t>
+  </si>
+  <si>
+    <t>Student Rating</t>
+  </si>
+  <si>
+    <t>Students</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Course.image.013811.png</t>
+  </si>
+  <si>
+    <t>Courses View</t>
+  </si>
+  <si>
+    <t>Time Table</t>
+  </si>
+  <si>
+    <t>dashboard_Images/13d34056.image.035329.png</t>
+  </si>
+  <si>
+    <t>CourseTimeTableView</t>
+  </si>
+  <si>
+    <t>Observation Qn</t>
+  </si>
+  <si>
+    <t>dashboard_Images/question.png</t>
+  </si>
+  <si>
+    <t>Obeservation Qns</t>
+  </si>
+  <si>
+    <t>Fee Summary</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Student Fees Summary.image.013944.png</t>
+  </si>
+  <si>
+    <t>Student Fee Summary</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Expense</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Expense.image.013510.png</t>
+  </si>
+  <si>
+    <t>Expenses View</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Staff Salary</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Staff Salary.image.013547.png</t>
+  </si>
+  <si>
+    <t>SalarySetup</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Student Fee.image.013619.png</t>
+  </si>
+  <si>
+    <t>Student Fee</t>
+  </si>
+  <si>
+    <t>Class Fee Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending Fees </t>
+  </si>
+  <si>
+    <t>dashboard_Images/df.image.080223.png</t>
+  </si>
+  <si>
+    <t>Student Fee Pending</t>
+  </si>
+  <si>
+    <t>Monthly Fee Summary</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Class Fees Summary.image.014040.png</t>
+  </si>
+  <si>
+    <t>Financial Summary</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Financial Summary.image.014121.png</t>
+  </si>
+  <si>
+    <t>Finance Summary</t>
+  </si>
+  <si>
+    <t>Expeses Summary</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Expeses Summary.image.014857.png</t>
+  </si>
+  <si>
+    <t>ExpeseSummery_Rpt</t>
+  </si>
+  <si>
+    <t>Manage</t>
+  </si>
+  <si>
+    <t>dashboard_Images/7ee0dee0.dash_image.060625.png</t>
+  </si>
+  <si>
+    <t>Student View</t>
+  </si>
+  <si>
+    <t>Assignments</t>
+  </si>
+  <si>
+    <t>dashboard_Images/80a95210.dash_image.065304.png</t>
+  </si>
+  <si>
+    <t>Student Activity</t>
+  </si>
+  <si>
+    <t>Attendance</t>
+  </si>
+  <si>
+    <t>dashboard_Images/df.image.111601.png</t>
+  </si>
+  <si>
+    <t>student att dash</t>
+  </si>
+  <si>
+    <t>Leave</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Student Leave.image.0133262.png</t>
+  </si>
+  <si>
+    <t>Student leave log</t>
+  </si>
+  <si>
+    <t>dashboard_Images/f23b0784.dash_image.091042.png</t>
+  </si>
+  <si>
+    <t>Collect Fee</t>
+  </si>
+  <si>
+    <t>dashboard_Images/collectFee.png</t>
+  </si>
+  <si>
+    <t>st_fee_Form</t>
+  </si>
+  <si>
+    <t>Fee Pending</t>
+  </si>
+  <si>
+    <t>dashboard_Images/question_st.png</t>
+  </si>
+  <si>
+    <t>Obeservations_st</t>
+  </si>
+  <si>
+    <t>Progress Card</t>
+  </si>
+  <si>
+    <t>dashboard_Images/da6bd0ad.dash_image.092247.png</t>
+  </si>
+  <si>
+    <t>Student Marks</t>
+  </si>
+  <si>
+    <t>dashboard_Images/dd.image.082709.png</t>
+  </si>
+  <si>
+    <t>Teachers View</t>
+  </si>
+  <si>
+    <t>Teachers</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>dashboard_Images/a0cd3bd7.image.041908.png</t>
+  </si>
+  <si>
+    <t>Teacher Activity</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>dashboard_Images/f4dbb49d.image.035921.png</t>
+  </si>
+  <si>
+    <t>dashboard_Images/abeebe66.image.040651.png</t>
+  </si>
+  <si>
+    <t>TeacherAttDash</t>
+  </si>
+  <si>
+    <t>dashboard_Images/fac3c273.image.035751.png</t>
+  </si>
+  <si>
+    <t>Teacher leave log</t>
+  </si>
+  <si>
+    <t>Schedule</t>
+  </si>
+  <si>
+    <t>Teacher Schedule</t>
+  </si>
+  <si>
+    <t>Teacher Dash View</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Courses</t>
+  </si>
+  <si>
+    <t>dashboard_Images/dss.image.082849.png</t>
+  </si>
+  <si>
+    <t>Course Dash</t>
+  </si>
+  <si>
+    <t>My Schedule</t>
+  </si>
+  <si>
+    <t>dashboard_Images/sd.image.082559.png</t>
+  </si>
+  <si>
+    <t>TeacherTimeTable</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Students.image.012707.png</t>
+  </si>
+  <si>
+    <t>Student Dash View</t>
+  </si>
+  <si>
+    <t>dashboard_Images/ff.image.082511.png</t>
+  </si>
+  <si>
+    <t>Finance Dash</t>
+  </si>
+  <si>
+    <t>My Task</t>
+  </si>
+  <si>
+    <t>dashboard_Images/df.image.081653.png</t>
+  </si>
+  <si>
+    <t>TODO</t>
+  </si>
+  <si>
+    <t>Course Attendance</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Course Attendance.image.060791.png</t>
+  </si>
+  <si>
+    <t>Student attendance by Course</t>
+  </si>
+  <si>
+    <t>Scan Attendance QR</t>
+  </si>
+  <si>
+    <t>dashboard_Images/ss.image.081803.png</t>
+  </si>
+  <si>
+    <t>ScanMyAttendance</t>
+  </si>
+  <si>
+    <t>Class Diary</t>
+  </si>
+  <si>
+    <t>dashboard_Images/1b10b898.dash_image.092006.png</t>
+  </si>
+  <si>
+    <t>ClassDiary</t>
+  </si>
+  <si>
+    <t>Holidays</t>
+  </si>
+  <si>
+    <t>dashboard_Images/sdsa.image.082204.png</t>
+  </si>
+  <si>
+    <t>Assingment</t>
+  </si>
+  <si>
+    <t>Class Assingment</t>
+  </si>
+  <si>
+    <t>My Students Marks</t>
+  </si>
+  <si>
+    <t>dashboard_Images/5fb3e3cc.image.042406.png</t>
+  </si>
+  <si>
+    <t>Teacher Student Marks</t>
+  </si>
+  <si>
+    <t>Student Diary</t>
+  </si>
+  <si>
+    <t>dashboard_Images/8df8cea3.image.084606.png</t>
+  </si>
+  <si>
+    <t>Teacher Rating</t>
+  </si>
+  <si>
+    <t>Parent Note</t>
+  </si>
+  <si>
+    <t>dashboard_Images/661276c6.dash_image.171435.png</t>
+  </si>
+  <si>
+    <t>FeedBack/Complaints</t>
+  </si>
+  <si>
+    <t>dashboard_Images/f4e38ab5.dash_image.064659.png</t>
+  </si>
+  <si>
+    <t>FeedBack</t>
+  </si>
+  <si>
+    <t>Enquiries</t>
+  </si>
+  <si>
+    <t>dashboard_Images/3eb53695.dash_image.092144.png</t>
+  </si>
+  <si>
+    <t>Handbook</t>
+  </si>
+  <si>
+    <t>dashboard_images/502d45f4.dash_image.182747.png</t>
+  </si>
+  <si>
+    <t>Meeting Notes</t>
+  </si>
+  <si>
+    <t>dashboard_Images/Meetin_Notes.png</t>
+  </si>
+  <si>
+    <t>Health Data</t>
+  </si>
+  <si>
+    <t>dashboard_Images/StudentMedical.png</t>
+  </si>
+  <si>
+    <t>Health_Record</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -405,11 +792,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -423,7 +810,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>11</v>
       </c>
@@ -439,6 +826,994 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>80486473</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>80486474</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>80486475</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>80186485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>80486079</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>80486476</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>80486477</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>80486478</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>80486479</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>80486480</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>80486481</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>80486482</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>80486483</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>80486484</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>80486485</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>80486486</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>80486487</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>80486488</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>804864891</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>80486489</v>
+      </c>
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>80286485</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>80486490</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>80486491</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>80486492</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" t="s">
+        <v>74</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>80486493</v>
+      </c>
+      <c r="B26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>80486494</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>80486495</v>
+      </c>
+      <c r="B28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>80486496</v>
+      </c>
+      <c r="B29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>80486497</v>
+      </c>
+      <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>80486498</v>
+      </c>
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>80486499</v>
+      </c>
+      <c r="B32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>80486500</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" t="s">
+        <v>87</v>
+      </c>
+      <c r="G33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>80486501</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>80486502</v>
+      </c>
+      <c r="B35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" t="s">
+        <v>100</v>
+      </c>
+      <c r="E35" t="s">
+        <v>87</v>
+      </c>
+      <c r="G35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>80486503</v>
+      </c>
+      <c r="B36" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>80486504</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>80486505</v>
+      </c>
+      <c r="B38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>80486506</v>
+      </c>
+      <c r="B39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>80486507</v>
+      </c>
+      <c r="B40" t="s">
+        <v>112</v>
+      </c>
+      <c r="C40" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" t="s">
+        <v>113</v>
+      </c>
+      <c r="E40" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>80486508</v>
+      </c>
+      <c r="B41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41" t="s">
+        <v>115</v>
+      </c>
+      <c r="D41" t="s">
+        <v>116</v>
+      </c>
+      <c r="E41" t="s">
+        <v>74</v>
+      </c>
+      <c r="G41">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>80486509</v>
+      </c>
+      <c r="B42" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" t="s">
+        <v>117</v>
+      </c>
+      <c r="E42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>80486510</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" t="s">
+        <v>119</v>
+      </c>
+      <c r="E43" t="s">
+        <v>74</v>
+      </c>
+      <c r="G43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>80486511</v>
+      </c>
+      <c r="B44" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" t="s">
+        <v>120</v>
+      </c>
+      <c r="E44" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>80486512</v>
+      </c>
+      <c r="B45" t="s">
+        <v>122</v>
+      </c>
+      <c r="C45" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" t="s">
+        <v>124</v>
+      </c>
+      <c r="E45" t="s">
+        <v>74</v>
+      </c>
+      <c r="G45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>80486513</v>
+      </c>
+      <c r="B46" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" t="s">
+        <v>125</v>
+      </c>
+      <c r="E46" t="s">
+        <v>87</v>
+      </c>
+      <c r="G46">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>80486514</v>
+      </c>
+      <c r="B47" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" t="s">
+        <v>128</v>
+      </c>
+      <c r="D47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E47" t="s">
+        <v>74</v>
+      </c>
+      <c r="G47">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>80486515</v>
+      </c>
+      <c r="B48" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" t="s">
+        <v>129</v>
+      </c>
+      <c r="E48" t="s">
+        <v>87</v>
+      </c>
+      <c r="G48">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>80486516</v>
+      </c>
+      <c r="B49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10817"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517DF6E1-421F-D749-BD52-2528B57319BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17260" yWindow="660" windowWidth="17300" windowHeight="20160" activeTab="2"/>
+    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="20160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="2" name="dashboard" state="visible" r:id="rId4"/>
-    <sheet sheetId="1" name="products" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="teachers" state="visible" r:id="rId6"/>
+    <sheet name="dashboard" sheetId="2" r:id="rId1"/>
+    <sheet name="products" sheetId="1" r:id="rId2"/>
+    <sheet name="teachers" sheetId="3" r:id="rId3"/>
+    <sheet name="employees" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="229">
   <si>
     <t>txid</t>
   </si>
@@ -643,65 +645,131 @@
   </si>
   <si>
     <t>2020-09-01</t>
+  </si>
+  <si>
+    <t>E001</t>
+  </si>
+  <si>
+    <t>E002</t>
+  </si>
+  <si>
+    <t>E003</t>
+  </si>
+  <si>
+    <t>E004</t>
+  </si>
+  <si>
+    <t>E005</t>
+  </si>
+  <si>
+    <t>E006</t>
+  </si>
+  <si>
+    <t>E007</t>
+  </si>
+  <si>
+    <t>E008</t>
+  </si>
+  <si>
+    <t>Driver</t>
+  </si>
+  <si>
+    <t>Lab Assistance</t>
+  </si>
+  <si>
+    <t>Conductor</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>Helper</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Employees</t>
+  </si>
+  <si>
+    <t>Employee View</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Accounting</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy hh:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mm-yyyy hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
-      <sz val="12"/>
       <name val="&quot;Google Sans&quot;"/>
     </font>
     <font>
+      <sz val="12"/>
       <color rgb="FF1F1F1F"/>
-      <sz val="12"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
+      <sz val="9"/>
       <color rgb="FF1F1F1F"/>
-      <sz val="9"/>
       <name val="&quot;Google Sans&quot;"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1079,59 +1147,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2">
-        <v>100</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="12.6640625" customHeight="1"/>
+  <dimension ref="A1:G59"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="12.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="54.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="40.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="12.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1154,7 +1184,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="3">
         <v>80486473</v>
       </c>
@@ -1175,7 +1205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="3">
         <v>80486474</v>
       </c>
@@ -1196,7 +1226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="3">
         <v>80486475</v>
       </c>
@@ -1217,7 +1247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="3">
         <v>80186485</v>
       </c>
@@ -1238,7 +1268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="3">
         <v>80486079</v>
       </c>
@@ -1261,7 +1291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="3">
         <v>80486476</v>
       </c>
@@ -1279,7 +1309,7 @@
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="3">
         <v>80486477</v>
       </c>
@@ -1297,7 +1327,7 @@
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="3">
         <v>80486478</v>
       </c>
@@ -1315,7 +1345,7 @@
       </c>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="3">
         <v>80486479</v>
       </c>
@@ -1333,7 +1363,7 @@
       </c>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="3">
         <v>80486480</v>
       </c>
@@ -1353,7 +1383,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="3">
         <v>80486481</v>
       </c>
@@ -1371,7 +1401,7 @@
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="3">
         <v>80486482</v>
       </c>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="3">
         <v>80486483</v>
       </c>
@@ -1407,7 +1437,7 @@
       </c>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="3">
         <v>80486484</v>
       </c>
@@ -1428,7 +1458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="3">
         <v>80486485</v>
       </c>
@@ -1449,7 +1479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="3">
         <v>80486486</v>
       </c>
@@ -1470,7 +1500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="3">
         <v>80486487</v>
       </c>
@@ -1491,7 +1521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="3">
         <v>80486488</v>
       </c>
@@ -1514,7 +1544,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16" customHeight="1">
       <c r="A20" s="3">
         <v>804864891</v>
       </c>
@@ -1537,7 +1567,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="3">
         <v>80486489</v>
       </c>
@@ -1560,7 +1590,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="3">
         <v>80286485</v>
       </c>
@@ -1581,7 +1611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="3">
         <v>80486490</v>
       </c>
@@ -1602,7 +1632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="3">
         <v>80486491</v>
       </c>
@@ -1623,7 +1653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="3">
         <v>80486492</v>
       </c>
@@ -1644,7 +1674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="3">
         <v>80486493</v>
       </c>
@@ -1665,7 +1695,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="3">
         <v>80486494</v>
       </c>
@@ -1686,7 +1716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="3">
         <v>80486495</v>
       </c>
@@ -1707,7 +1737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="3">
         <v>80486496</v>
       </c>
@@ -1728,7 +1758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="3">
         <v>80486497</v>
       </c>
@@ -1749,18 +1779,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="3">
-        <v>80486498</v>
+        <v>804864971</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>14</v>
+        <v>223</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>84</v>
+        <v>224</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>82</v>
@@ -1770,395 +1800,408 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="3">
-        <v>80486499</v>
+        <v>80486498</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>82</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="3">
-        <v>80486500</v>
+        <v>80486499</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>82</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="3">
-        <v>80486501</v>
+        <v>80486500</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="F34" s="4"/>
       <c r="G34" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1">
       <c r="A35" s="3">
-        <v>80486502</v>
+        <v>80486501</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F35" s="4"/>
+      <c r="F35" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="G35" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" customHeight="1">
       <c r="A36" s="3">
-        <v>80486503</v>
+        <v>80486502</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" customHeight="1">
       <c r="A37" s="3">
-        <v>80486504</v>
+        <v>80486503</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1">
       <c r="A38" s="3">
-        <v>80486505</v>
+        <v>80486504</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1">
       <c r="A39" s="3">
-        <v>80486506</v>
+        <v>80486505</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" customHeight="1">
       <c r="A40" s="3">
-        <v>80486507</v>
+        <v>80486506</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>49</v>
+        <v>104</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1">
       <c r="A41" s="3">
-        <v>80486508</v>
+        <v>80486507</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" customHeight="1">
       <c r="A42" s="3">
-        <v>80486509</v>
+        <v>80486508</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="F42" s="4"/>
       <c r="G42" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.75" customHeight="1">
       <c r="A43" s="3">
-        <v>80486510</v>
+        <v>80486509</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A44" s="3">
+        <v>80486510</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>80486511</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>115</v>
+      <c r="C44" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="F44" s="4"/>
       <c r="G44" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="15.75" customHeight="1">
       <c r="A45" s="3">
-        <v>80486512</v>
+        <v>80486511</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="F45" s="4"/>
       <c r="G45" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="16" customHeight="1">
+      <c r="A46" s="3">
+        <v>80486512</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F46" s="4"/>
+      <c r="G46" s="3">
         <v>12</v>
       </c>
     </row>
-    <row r="46" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+    <row r="47" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A47" s="3">
         <v>80486513</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B47" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C47" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
-        <v>80486514</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="16" customHeight="1">
       <c r="A48" s="3">
-        <v>80486515</v>
+        <v>80486514</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>82</v>
+        <v>121</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15.75" customHeight="1">
       <c r="A49" s="3">
-        <v>80486516</v>
+        <v>80486515</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A50" s="3">
+        <v>80486516</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
       <c r="F50" s="3"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G50" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.75" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2166,23 +2209,23 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="15.75" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="7"/>
+      <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="15.75" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
+      <c r="D53" s="7"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="15.75" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2190,7 +2233,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="15.75" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2198,7 +2241,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="15.75" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2206,7 +2249,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="15.75" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -2214,7 +2257,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="15.75" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -2222,15 +2265,62 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
+    <row r="59" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -2243,7 +2333,7 @@
     <col min="9" max="9" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2281,7 +2371,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>143</v>
       </c>
@@ -2311,13 +2401,13 @@
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="8">
-        <v>46027.8771412037</v>
+        <v>46027.877141203702</v>
       </c>
       <c r="M2" s="3">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>152</v>
       </c>
@@ -2353,7 +2443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>161</v>
       </c>
@@ -2389,7 +2479,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>169</v>
       </c>
@@ -2419,13 +2509,13 @@
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="8">
-        <v>45390.73857638889</v>
+        <v>45390.738576388889</v>
       </c>
       <c r="M5" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>177</v>
       </c>
@@ -2461,7 +2551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>185</v>
       </c>
@@ -2491,13 +2581,13 @@
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="9">
-        <v>45367.33456018519</v>
+        <v>45367.334560185191</v>
       </c>
       <c r="M7" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>193</v>
       </c>
@@ -2527,13 +2617,13 @@
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="9">
-        <v>45376.92606481482</v>
+        <v>45376.926064814819</v>
       </c>
       <c r="M8" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>201</v>
       </c>
@@ -2569,24 +2659,392 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13">
       <c r="K10" s="3"/>
       <c r="L10" s="8"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13">
       <c r="K11" s="3"/>
       <c r="L11" s="8"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13">
       <c r="K12" s="3"/>
     </row>
-    <row r="13" spans="11:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13">
       <c r="K13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{839E3EAF-C715-9846-B514-B1C61E11B8D0}">
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="35" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J1" t="s">
+        <v>139</v>
+      </c>
+      <c r="L1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" t="s">
+        <v>149</v>
+      </c>
+      <c r="J2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="8">
+        <v>46027.877141203702</v>
+      </c>
+      <c r="N2" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="8">
+        <v>45388.465219907404</v>
+      </c>
+      <c r="N3" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J4" t="s">
+        <v>168</v>
+      </c>
+      <c r="L4" s="3"/>
+      <c r="M4" s="8">
+        <v>45473.821851851855</v>
+      </c>
+      <c r="N4" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" t="s">
+        <v>226</v>
+      </c>
+      <c r="D5" t="s">
+        <v>218</v>
+      </c>
+      <c r="E5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J5" t="s">
+        <v>176</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="8">
+        <v>45390.738576388889</v>
+      </c>
+      <c r="N5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F6" t="s">
+        <v>181</v>
+      </c>
+      <c r="G6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J6" t="s">
+        <v>184</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="8">
+        <v>46024.33793981481</v>
+      </c>
+      <c r="N6" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E7" t="s">
+        <v>188</v>
+      </c>
+      <c r="F7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H7" t="s">
+        <v>149</v>
+      </c>
+      <c r="J7" t="s">
+        <v>192</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="9">
+        <v>45367.334560185191</v>
+      </c>
+      <c r="N7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" t="s">
+        <v>196</v>
+      </c>
+      <c r="F8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G8" t="s">
+        <v>198</v>
+      </c>
+      <c r="H8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J8" t="s">
+        <v>200</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="9">
+        <v>45376.926064814819</v>
+      </c>
+      <c r="N8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" t="s">
+        <v>221</v>
+      </c>
+      <c r="E9" t="s">
+        <v>204</v>
+      </c>
+      <c r="F9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G9" t="s">
+        <v>206</v>
+      </c>
+      <c r="H9" t="s">
+        <v>158</v>
+      </c>
+      <c r="J9" t="s">
+        <v>208</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="8">
+        <v>45789.925162037034</v>
+      </c>
+      <c r="N9" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="L10" s="3"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="L11" s="3"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="L13" s="3"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3320" uniqueCount="1748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3346" uniqueCount="1762">
   <si>
     <t>id</t>
   </si>
@@ -4577,6 +4577,9 @@
     <t>27/Feb/2024</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>2026-08-28T04:49:30.255Z</t>
   </si>
   <si>
@@ -4607,22 +4610,61 @@
     <t>paymentMode</t>
   </si>
   <si>
-    <t>7ef352c0-f980-4dfa-b8eb-46139e900b9d</t>
-  </si>
-  <si>
-    <t>st/fe/20260830232863</t>
-  </si>
-  <si>
-    <t>30/Aug/2026</t>
-  </si>
-  <si>
-    <t>no remark</t>
-  </si>
-  <si>
-    <t>2026-08-30T18:02:31.413Z</t>
+    <t>733ca5a9-a4cf-43e6-87f7-187f9303e369</t>
+  </si>
+  <si>
+    <t>st/fe/260831180889</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-31T12:39:15.277Z</t>
   </si>
   <si>
     <t>Paid</t>
+  </si>
+  <si>
+    <t>9c81a983-ab28-4e4b-b0dd-28c8129b0a88</t>
+  </si>
+  <si>
+    <t>st/fe/260831181864</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-08-31T12:49:26.640Z</t>
+  </si>
+  <si>
+    <t>94098108-61aa-49b4-9305-fce5648c31bb</t>
+  </si>
+  <si>
+    <t>st/fe/260831182605</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-31T12:57:44.877Z</t>
+  </si>
+  <si>
+    <t>b9b3a95f-50cf-4791-b191-31a4b030ae4c</t>
+  </si>
+  <si>
+    <t>st/fe/260831182790</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-08-31T12:58:03.126Z</t>
   </si>
   <si>
     <t>acyear</t>
@@ -6981,31 +7023,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>1684</v>
+        <v>1698</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>1685</v>
+        <v>1699</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>1686</v>
+        <v>1700</v>
       </c>
       <c r="E1" s="32" t="s">
-        <v>1687</v>
+        <v>1701</v>
       </c>
       <c r="F1" s="32" t="s">
-        <v>1688</v>
+        <v>1702</v>
       </c>
       <c r="G1" s="32" t="s">
-        <v>1689</v>
+        <v>1703</v>
       </c>
       <c r="H1" s="32" t="s">
-        <v>1690</v>
+        <v>1704</v>
       </c>
       <c r="I1" s="32" t="s">
-        <v>1691</v>
+        <v>1705</v>
       </c>
       <c r="J1" s="32" t="s">
-        <v>1692</v>
+        <v>1706</v>
       </c>
       <c r="K1" s="32" t="s">
         <v>275</v>
@@ -7019,117 +7061,117 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>1693</v>
+        <v>1707</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>1694</v>
+        <v>1708</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>1695</v>
+        <v>1709</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>1696</v>
+        <v>1710</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>1697</v>
+        <v>1711</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>1698</v>
+        <v>1712</v>
       </c>
       <c r="G2" s="32" t="s">
-        <v>1699</v>
+        <v>1713</v>
       </c>
       <c r="H2" s="32" t="s">
-        <v>1700</v>
+        <v>1714</v>
       </c>
       <c r="I2" s="32" t="s">
-        <v>1701</v>
+        <v>1715</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>1702</v>
+        <v>1716</v>
       </c>
       <c r="K2" s="32" t="s">
-        <v>1703</v>
+        <v>1717</v>
       </c>
       <c r="L2" s="32"/>
       <c r="M2" s="32" t="s">
-        <v>1704</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>1705</v>
+        <v>1719</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>1706</v>
+        <v>1720</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>1695</v>
+        <v>1709</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>1707</v>
+        <v>1721</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>211</v>
       </c>
       <c r="F3" s="32" t="s">
-        <v>1708</v>
+        <v>1722</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>1709</v>
+        <v>1723</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>1710</v>
+        <v>1724</v>
       </c>
       <c r="I3" s="32" t="s">
-        <v>1711</v>
+        <v>1725</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>1712</v>
+        <v>1726</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>1713</v>
+        <v>1727</v>
       </c>
       <c r="L3" s="32"/>
       <c r="M3" s="32" t="s">
-        <v>1714</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>1715</v>
+        <v>1729</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>1716</v>
+        <v>1730</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>1695</v>
+        <v>1709</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>1717</v>
+        <v>1731</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>1718</v>
+        <v>1732</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>1719</v>
+        <v>1733</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>1720</v>
+        <v>1734</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>1721</v>
+        <v>1735</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>1722</v>
+        <v>1736</v>
       </c>
       <c r="J4" s="32"/>
       <c r="K4" s="32" t="s">
-        <v>1723</v>
+        <v>1737</v>
       </c>
       <c r="L4" s="32"/>
       <c r="M4" s="32" t="s">
-        <v>1724</v>
+        <v>1738</v>
       </c>
     </row>
   </sheetData>
@@ -41281,19 +41323,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1725</v>
+        <v>1739</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1726</v>
+        <v>1740</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1727</v>
+        <v>1741</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1728</v>
+        <v>1742</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>1729</v>
+        <v>1743</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>379</v>
@@ -41305,34 +41347,34 @@
         <v>279</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>1730</v>
+        <v>1744</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>1731</v>
+        <v>1745</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1732</v>
+        <v>1746</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1733</v>
+        <v>1747</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1734</v>
+        <v>1748</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1735</v>
+        <v>1749</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>1736</v>
+        <v>1750</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>1737</v>
+        <v>1751</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>1738</v>
+        <v>1752</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>1739</v>
+        <v>1753</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>380</v>
@@ -41378,19 +41420,19 @@
     <row r="7" ht="14" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="14" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>1740</v>
+        <v>1754</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1741</v>
+        <v>1755</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1282</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="N8" s="1">
         <v>121</v>
@@ -41399,36 +41441,36 @@
         <v>12</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>1743</v>
+        <v>1757</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>1744</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>1745</v>
+        <v>1759</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1746</v>
+        <v>1760</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>1282</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="N9" s="1">
         <v>22</v>
@@ -41437,19 +41479,19 @@
         <v>22</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>1743</v>
+        <v>1757</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>1742</v>
+        <v>1756</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>1747</v>
+        <v>1761</v>
       </c>
     </row>
   </sheetData>
@@ -41459,33 +41501,33 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="G1" s="29" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="I1" s="28" t="s">
         <v>379</v>
@@ -41502,37 +41544,130 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B2" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C2" t="s">
-        <v>1282</v>
+        <v>1509</v>
       </c>
       <c r="D2" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="F2">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="G2" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="H2" t="s">
         <v>153</v>
       </c>
-      <c r="I2" t="s">
-        <v>1528</v>
-      </c>
       <c r="J2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C3" t="s">
+        <v>880</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F3">
+        <v>3000</v>
+      </c>
+      <c r="G3" t="s">
         <v>1529</v>
       </c>
-      <c r="L2" t="s">
-        <v>1530</v>
+      <c r="H3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4">
+        <v>3000</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1539</v>
+      </c>
+      <c r="H4" t="s">
+        <v>168</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F5">
+        <v>1500</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1543</v>
+      </c>
+      <c r="H5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1544</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1531</v>
       </c>
     </row>
   </sheetData>
@@ -49680,7 +49815,7 @@
         <v>45789</v>
       </c>
     </row>
-    <row r="131" ht="14" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="131" ht="14" customHeight="1" hidden="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>1281</v>
       </c>
@@ -51427,7 +51562,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="164" ht="14" customHeight="1" hidden="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" ht="14" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
         <v>1508</v>
       </c>
@@ -51461,26 +51596,25 @@
         <v>803</v>
       </c>
       <c r="M164" s="3" t="s">
-        <v>449</v>
+        <v>1515</v>
       </c>
       <c r="N164" s="3" t="s">
-        <v>449</v>
+        <v>1515</v>
       </c>
       <c r="O164" s="12" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="P164" s="3">
         <v>1</v>
       </c>
       <c r="Q164" s="3" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="R164" s="15" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T164"/>
   <hyperlinks>
     <hyperlink ref="J131" r:id="rId1"/>
   </hyperlinks>
@@ -51506,25 +51640,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>1531</v>
+        <v>1545</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>1532</v>
+        <v>1546</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>1533</v>
+        <v>1547</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>1534</v>
+        <v>1548</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>177</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>1535</v>
+        <v>1549</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>1536</v>
+        <v>1550</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>380</v>
@@ -51535,10 +51669,10 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1537</v>
+        <v>1551</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>448</v>
@@ -51550,7 +51684,7 @@
         <v>255</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G2" s="16">
         <v>0.40625</v>
@@ -51567,10 +51701,10 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1540</v>
+        <v>1554</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>448</v>
@@ -51582,7 +51716,7 @@
         <v>211</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G3" s="16">
         <v>0.45138888889050577</v>
@@ -51599,10 +51733,10 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1542</v>
+        <v>1556</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>448</v>
@@ -51614,7 +51748,7 @@
         <v>211</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G4" s="16">
         <v>0.4930555555547471</v>
@@ -51631,10 +51765,10 @@
     </row>
     <row r="5" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>1543</v>
+        <v>1557</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>448</v>
@@ -51663,10 +51797,10 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>448</v>
@@ -51678,7 +51812,7 @@
         <v>211</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G6" s="16">
         <v>0.5902777777773736</v>
@@ -51695,10 +51829,10 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>1545</v>
+        <v>1559</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>448</v>
@@ -51710,7 +51844,7 @@
         <v>253</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G7" s="16">
         <v>0.40625</v>
@@ -51727,10 +51861,10 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>1546</v>
+        <v>1560</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>448</v>
@@ -51742,7 +51876,7 @@
         <v>255</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G8" s="16">
         <v>0.45138888889050577</v>
@@ -51759,10 +51893,10 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>1547</v>
+        <v>1561</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>448</v>
@@ -51774,7 +51908,7 @@
         <v>253</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G9" s="16">
         <v>0.06597222222262644</v>
@@ -51791,10 +51925,10 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1548</v>
+        <v>1562</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>448</v>
@@ -51806,7 +51940,7 @@
         <v>255</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G10" s="16">
         <v>0.4930555555547471</v>
@@ -51823,10 +51957,10 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1549</v>
+        <v>1563</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>448</v>
@@ -51838,7 +51972,7 @@
         <v>250</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G11" s="16">
         <v>0.5902777777773736</v>
@@ -51855,10 +51989,10 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1551</v>
+        <v>1565</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>448</v>
@@ -51870,7 +52004,7 @@
         <v>250</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G12" s="16">
         <v>0.40625</v>
@@ -51887,10 +52021,10 @@
     </row>
     <row r="13" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>1552</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>1538</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>448</v>
@@ -51902,7 +52036,7 @@
         <v>253</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G13" s="16">
         <v>0.45138888889050577</v>
@@ -51919,10 +52053,10 @@
     </row>
     <row r="14" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1553</v>
+        <v>1567</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>448</v>
@@ -51934,7 +52068,7 @@
         <v>253</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G14" s="16">
         <v>0.4930555555547471</v>
@@ -51951,10 +52085,10 @@
     </row>
     <row r="15" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1554</v>
+        <v>1568</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>448</v>
@@ -51966,7 +52100,7 @@
         <v>262</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G15" s="16">
         <v>0.5659722222226264</v>
@@ -51983,10 +52117,10 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>1555</v>
+        <v>1569</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>448</v>
@@ -51998,7 +52132,7 @@
         <v>200</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G16" s="16">
         <v>0.5902777777773736</v>
@@ -52015,10 +52149,10 @@
     </row>
     <row r="17" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>1556</v>
+        <v>1570</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>448</v>
@@ -52030,7 +52164,7 @@
         <v>258</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G17" s="16">
         <v>0.40625</v>
@@ -52047,10 +52181,10 @@
     </row>
     <row r="18" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>1557</v>
+        <v>1571</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>448</v>
@@ -52062,7 +52196,7 @@
         <v>211</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G18" s="16">
         <v>0.45138888889050577</v>
@@ -52079,10 +52213,10 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>1558</v>
+        <v>1572</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>448</v>
@@ -52094,7 +52228,7 @@
         <v>211</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G19" s="16">
         <v>0.4930555555547471</v>
@@ -52111,10 +52245,10 @@
     </row>
     <row r="20" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>1559</v>
+        <v>1573</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>448</v>
@@ -52126,7 +52260,7 @@
         <v>255</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G20" s="16">
         <v>0.5659722222226264</v>
@@ -52143,10 +52277,10 @@
     </row>
     <row r="21" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>1560</v>
+        <v>1574</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>448</v>
@@ -52175,10 +52309,10 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>1561</v>
+        <v>1575</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>448</v>
@@ -52207,10 +52341,10 @@
     </row>
     <row r="23" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>1562</v>
+        <v>1576</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>448</v>
@@ -52222,7 +52356,7 @@
         <v>250</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G23" s="16">
         <v>0.45138888889050577</v>
@@ -52239,10 +52373,10 @@
     </row>
     <row r="24" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>1563</v>
+        <v>1577</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>448</v>
@@ -52254,7 +52388,7 @@
         <v>211</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G24" s="16">
         <v>0.4930555555547471</v>
@@ -52271,10 +52405,10 @@
     </row>
     <row r="25" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>1564</v>
+        <v>1578</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>448</v>
@@ -52286,7 +52420,7 @@
         <v>250</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G25" s="16">
         <v>0.5659722222226264</v>
@@ -52303,10 +52437,10 @@
     </row>
     <row r="26" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>1565</v>
+        <v>1579</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>448</v>
@@ -52318,7 +52452,7 @@
         <v>246</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G26" s="16">
         <v>0.5902777777773736</v>
@@ -52335,10 +52469,10 @@
     </row>
     <row r="27" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>1566</v>
+        <v>1580</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>598</v>
@@ -52350,7 +52484,7 @@
         <v>211</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G27" s="16">
         <v>0.40625</v>
@@ -52367,10 +52501,10 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>1567</v>
+        <v>1581</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>598</v>
@@ -52399,10 +52533,10 @@
     </row>
     <row r="29" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>1568</v>
+        <v>1582</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>598</v>
@@ -52414,7 +52548,7 @@
         <v>255</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G29" s="16">
         <v>0.4895833333321207</v>
@@ -52431,10 +52565,10 @@
     </row>
     <row r="30" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>1569</v>
+        <v>1583</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>598</v>
@@ -52446,7 +52580,7 @@
         <v>211</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G30" s="16">
         <v>0.5659722222226264</v>
@@ -52463,10 +52597,10 @@
     </row>
     <row r="31" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>1570</v>
+        <v>1584</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>598</v>
@@ -52495,10 +52629,10 @@
     </row>
     <row r="32" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>598</v>
@@ -52527,10 +52661,10 @@
     </row>
     <row r="33" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>1572</v>
+        <v>1586</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>598</v>
@@ -52542,7 +52676,7 @@
         <v>211</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G33" s="16">
         <v>0.45138888889050577</v>
@@ -52559,10 +52693,10 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>1573</v>
+        <v>1587</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>598</v>
@@ -52574,7 +52708,7 @@
         <v>211</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G34" s="16">
         <v>0.5659722222226264</v>
@@ -52591,10 +52725,10 @@
     </row>
     <row r="35" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>1574</v>
+        <v>1588</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>598</v>
@@ -52606,7 +52740,7 @@
         <v>255</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G35" s="16">
         <v>0.59375</v>
@@ -52623,10 +52757,10 @@
     </row>
     <row r="36" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>598</v>
@@ -52638,7 +52772,7 @@
         <v>255</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G36" s="16">
         <v>0.40625</v>
@@ -52655,10 +52789,10 @@
     </row>
     <row r="37" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>1576</v>
+        <v>1590</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>598</v>
@@ -52687,10 +52821,10 @@
     </row>
     <row r="38" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>1577</v>
+        <v>1591</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>598</v>
@@ -52719,10 +52853,10 @@
     </row>
     <row r="39" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>598</v>
@@ -52734,7 +52868,7 @@
         <v>200</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G39" s="16">
         <v>0.5659722222226264</v>
@@ -52751,10 +52885,10 @@
     </row>
     <row r="40" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>1579</v>
+        <v>1593</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>598</v>
@@ -52766,7 +52900,7 @@
         <v>262</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G40" s="16">
         <v>0.59375</v>
@@ -52783,10 +52917,10 @@
     </row>
     <row r="41" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>1580</v>
+        <v>1594</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>598</v>
@@ -52798,7 +52932,7 @@
         <v>255</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G41" s="16">
         <v>0.40625</v>
@@ -52815,10 +52949,10 @@
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>1581</v>
+        <v>1595</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>598</v>
@@ -52830,7 +52964,7 @@
         <v>211</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G42" s="16">
         <v>0.45138888889050577</v>
@@ -52847,10 +52981,10 @@
     </row>
     <row r="43" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>1582</v>
+        <v>1596</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>598</v>
@@ -52879,10 +53013,10 @@
     </row>
     <row r="44" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>1583</v>
+        <v>1597</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>598</v>
@@ -52894,7 +53028,7 @@
         <v>255</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G44" s="16">
         <v>0.59375</v>
@@ -52911,10 +53045,10 @@
     </row>
     <row r="45" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>1584</v>
+        <v>1598</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>598</v>
@@ -52926,7 +53060,7 @@
         <v>258</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G45" s="16">
         <v>0.40625</v>
@@ -52943,10 +53077,10 @@
     </row>
     <row r="46" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>1585</v>
+        <v>1599</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>598</v>
@@ -52975,10 +53109,10 @@
     </row>
     <row r="47" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>1586</v>
+        <v>1600</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>598</v>
@@ -53007,10 +53141,10 @@
     </row>
     <row r="48" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>1587</v>
+        <v>1601</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>598</v>
@@ -53022,7 +53156,7 @@
         <v>255</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G48" s="16">
         <v>0.4895833333321207</v>
@@ -53039,10 +53173,10 @@
     </row>
     <row r="49" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>1588</v>
+        <v>1602</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>598</v>
@@ -53054,7 +53188,7 @@
         <v>246</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G49" s="16">
         <v>0.59375</v>
@@ -53071,10 +53205,10 @@
     </row>
     <row r="50" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>1589</v>
+        <v>1603</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>554</v>
@@ -53086,7 +53220,7 @@
         <v>250</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G50" s="16">
         <v>0.45138888889050577</v>
@@ -53103,10 +53237,10 @@
     </row>
     <row r="51" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>1590</v>
+        <v>1604</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>554</v>
@@ -53135,10 +53269,10 @@
     </row>
     <row r="52" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>1591</v>
+        <v>1605</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>554</v>
@@ -53167,10 +53301,10 @@
     </row>
     <row r="53" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>1592</v>
+        <v>1606</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>554</v>
@@ -53182,7 +53316,7 @@
         <v>262</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G53" s="16">
         <v>0.4895833333321207</v>
@@ -53199,10 +53333,10 @@
     </row>
     <row r="54" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>1593</v>
+        <v>1607</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>554</v>
@@ -53214,7 +53348,7 @@
         <v>250</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G54" s="16">
         <v>0.45138888889050577</v>
@@ -53231,10 +53365,10 @@
     </row>
     <row r="55" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>1594</v>
+        <v>1608</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>554</v>
@@ -53246,7 +53380,7 @@
         <v>211</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G55" s="16">
         <v>0.4895833333321207</v>
@@ -53263,10 +53397,10 @@
     </row>
     <row r="56" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>1595</v>
+        <v>1609</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>554</v>
@@ -53295,10 +53429,10 @@
     </row>
     <row r="57" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>1596</v>
+        <v>1610</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>554</v>
@@ -53310,7 +53444,7 @@
         <v>255</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G57" s="16">
         <v>0.4895833333321207</v>
@@ -53327,10 +53461,10 @@
     </row>
     <row r="58" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>1597</v>
+        <v>1611</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>554</v>
@@ -53342,7 +53476,7 @@
         <v>255</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G58" s="16">
         <v>0.45138888889050577</v>
@@ -53359,10 +53493,10 @@
     </row>
     <row r="59" ht="15.75" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>1598</v>
+        <v>1612</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>554</v>
@@ -53374,7 +53508,7 @@
         <v>246</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G59" s="16">
         <v>0.4895833333321207</v>
@@ -53391,10 +53525,10 @@
     </row>
     <row r="60" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>1599</v>
+        <v>1613</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>554</v>
@@ -53403,7 +53537,7 @@
         <v>162</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>393</v>
@@ -53423,10 +53557,10 @@
     </row>
     <row r="61" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>1601</v>
+        <v>1615</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>554</v>
@@ -53435,10 +53569,10 @@
         <v>176</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G61" s="16">
         <v>0.3958333333321207</v>
@@ -53455,10 +53589,10 @@
     </row>
     <row r="62" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>1602</v>
+        <v>1616</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>554</v>
@@ -53487,10 +53621,10 @@
     </row>
     <row r="63" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>1603</v>
+        <v>1617</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>554</v>
@@ -53499,7 +53633,7 @@
         <v>198</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>393</v>
@@ -53519,10 +53653,10 @@
     </row>
     <row r="64" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>1604</v>
+        <v>1618</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>554</v>
@@ -53531,10 +53665,10 @@
         <v>209</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G64" s="16">
         <v>0.3958333333321207</v>
@@ -53551,10 +53685,10 @@
     </row>
     <row r="65" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>1605</v>
+        <v>1619</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>811</v>
@@ -53563,7 +53697,7 @@
         <v>162</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>393</v>
@@ -53583,10 +53717,10 @@
     </row>
     <row r="66" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>1606</v>
+        <v>1620</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>811</v>
@@ -53598,7 +53732,7 @@
         <v>255</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G66" s="16">
         <v>0.45138888889050577</v>
@@ -53615,10 +53749,10 @@
     </row>
     <row r="67" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>1607</v>
+        <v>1621</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>811</v>
@@ -53630,7 +53764,7 @@
         <v>250</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G67" s="16">
         <v>0.4930555555547471</v>
@@ -53647,10 +53781,10 @@
     </row>
     <row r="68" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>1608</v>
+        <v>1622</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>811</v>
@@ -53659,10 +53793,10 @@
         <v>176</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G68" s="16">
         <v>0.3958333333321207</v>
@@ -53679,10 +53813,10 @@
     </row>
     <row r="69" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>1609</v>
+        <v>1623</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>811</v>
@@ -53694,7 +53828,7 @@
         <v>262</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G69" s="16">
         <v>0.45138888889050577</v>
@@ -53711,10 +53845,10 @@
     </row>
     <row r="70" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>1610</v>
+        <v>1624</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>811</v>
@@ -53743,10 +53877,10 @@
     </row>
     <row r="71" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>1611</v>
+        <v>1625</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>811</v>
@@ -53775,10 +53909,10 @@
     </row>
     <row r="72" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>1612</v>
+        <v>1626</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>811</v>
@@ -53790,7 +53924,7 @@
         <v>211</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G72" s="16">
         <v>0.45138888889050577</v>
@@ -53807,10 +53941,10 @@
     </row>
     <row r="73" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>1613</v>
+        <v>1627</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>811</v>
@@ -53822,7 +53956,7 @@
         <v>250</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G73" s="16">
         <v>0.4895833333321207</v>
@@ -53839,10 +53973,10 @@
     </row>
     <row r="74" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>1614</v>
+        <v>1628</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>811</v>
@@ -53851,7 +53985,7 @@
         <v>198</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>393</v>
@@ -53871,10 +54005,10 @@
     </row>
     <row r="75" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>1615</v>
+        <v>1629</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>811</v>
@@ -53886,7 +54020,7 @@
         <v>255</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G75" s="16">
         <v>0.45138888889050577</v>
@@ -53903,10 +54037,10 @@
     </row>
     <row r="76" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>1616</v>
+        <v>1630</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>811</v>
@@ -53935,10 +54069,10 @@
     </row>
     <row r="77" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>1617</v>
+        <v>1631</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>811</v>
@@ -53947,10 +54081,10 @@
         <v>209</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>1600</v>
+        <v>1614</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G77" s="16">
         <v>0.3958333333321207</v>
@@ -53967,10 +54101,10 @@
     </row>
     <row r="78" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>1618</v>
+        <v>1632</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>811</v>
@@ -53982,7 +54116,7 @@
         <v>246</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="G78" s="16">
         <v>0.45138888889050577</v>
@@ -53999,10 +54133,10 @@
     </row>
     <row r="79" ht="14" customHeight="1" hidden="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>1619</v>
+        <v>1633</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>811</v>
@@ -54056,34 +54190,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1620</v>
+        <v>1634</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1621</v>
+        <v>1635</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1622</v>
+        <v>1636</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1623</v>
+        <v>1637</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>1624</v>
+        <v>1638</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>1625</v>
+        <v>1639</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>1626</v>
+        <v>1640</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>1628</v>
+        <v>1642</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>1629</v>
+        <v>1643</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>380</v>
@@ -54094,13 +54228,13 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1630</v>
+        <v>1644</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1631</v>
+        <v>1645</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1632</v>
+        <v>1646</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>246</v>
@@ -54133,16 +54267,16 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1633</v>
+        <v>1647</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1634</v>
+        <v>1648</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1635</v>
+        <v>1649</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1636</v>
+        <v>1650</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>172</v>
@@ -54172,22 +54306,22 @@
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1637</v>
+        <v>1651</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1638</v>
+        <v>1652</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1639</v>
+        <v>1653</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1640</v>
+        <v>1654</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>172</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1550</v>
+        <v>1564</v>
       </c>
       <c r="G4" s="30">
         <v>1000</v>
@@ -54211,16 +54345,16 @@
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>1641</v>
+        <v>1655</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1642</v>
+        <v>1656</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1643</v>
+        <v>1657</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1644</v>
+        <v>1658</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>172</v>
@@ -54241,7 +54375,7 @@
         <v>1700</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>1645</v>
+        <v>1659</v>
       </c>
       <c r="M5" s="3">
         <v>7</v>
@@ -54249,22 +54383,22 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>1646</v>
+        <v>1660</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>1647</v>
+        <v>1661</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1648</v>
+        <v>1662</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1649</v>
+        <v>1663</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>172</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G6" s="30">
         <v>1000</v>
@@ -54287,16 +54421,16 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>1650</v>
+        <v>1664</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>191</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1651</v>
+        <v>1665</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1652</v>
+        <v>1666</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>172</v>
@@ -54325,16 +54459,16 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>1653</v>
+        <v>1667</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1654</v>
+        <v>1668</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1655</v>
+        <v>1669</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1656</v>
+        <v>1670</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>172</v>
@@ -54363,22 +54497,22 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>1657</v>
+        <v>1671</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1658</v>
+        <v>1672</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1659</v>
+        <v>1673</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1660</v>
+        <v>1674</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>172</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G9" s="30">
         <v>1000</v>
@@ -54401,13 +54535,13 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>1661</v>
+        <v>1675</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1662</v>
+        <v>1676</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1663</v>
+        <v>1677</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>246</v>
@@ -54439,13 +54573,13 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>1664</v>
+        <v>1678</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1659</v>
+        <v>1673</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1665</v>
+        <v>1679</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>246</v>
@@ -54477,22 +54611,22 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>1666</v>
+        <v>1680</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1667</v>
+        <v>1681</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1668</v>
+        <v>1682</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1660</v>
+        <v>1674</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>172</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G12" s="30">
         <v>1000</v>
@@ -54515,22 +54649,22 @@
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>1669</v>
+        <v>1683</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1638</v>
+        <v>1652</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1670</v>
+        <v>1684</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1671</v>
+        <v>1685</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>195</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="G13" s="30">
         <v>1000</v>
@@ -60507,7 +60641,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>1672</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -60515,7 +60649,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1673</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -60523,7 +60657,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1674</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -60531,7 +60665,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -60539,7 +60673,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>1676</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -60547,7 +60681,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1677</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -60555,7 +60689,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1678</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -60563,7 +60697,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -60571,7 +60705,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1680</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -60579,7 +60713,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1681</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -60587,7 +60721,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>1682</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -60595,7 +60729,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>1683</v>
+        <v>1697</v>
       </c>
     </row>
   </sheetData>

--- a/data/database.xlsx
+++ b/data/database.xlsx
@@ -4,27 +4,28 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="20160" firstSheet="2" activeTab="16"/>
+    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="20160" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="dashboard" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="reftbl" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="products" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="products" state="hidden" r:id="rId6"/>
     <sheet sheetId="4" name="staff" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="employees" state="hidden" r:id="rId8"/>
     <sheet sheetId="6" name="teachers" state="hidden" r:id="rId9"/>
-    <sheet sheetId="7" name="staffpay" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="StaffAttendanceLog" state="visible" r:id="rId11"/>
+    <sheet sheetId="7" name="staffpay" state="hidden" r:id="rId10"/>
+    <sheet sheetId="8" name="StaffAttendanceLog" state="hidden" r:id="rId11"/>
     <sheet sheetId="9" name="students" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="stfee" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="coursetimetbl" state="visible" r:id="rId14"/>
+    <sheet sheetId="10" name="stfee" state="hidden" r:id="rId13"/>
+    <sheet sheetId="11" name="coursetimetbl" state="hidden" r:id="rId14"/>
     <sheet sheetId="12" name="courses" state="visible" r:id="rId15"/>
     <sheet sheetId="13" name="handbook" state="visible" r:id="rId16"/>
-    <sheet sheetId="14" name="feedback" state="visible" r:id="rId17"/>
-    <sheet sheetId="15" name="StudentAttendanceLog" state="visible" r:id="rId18"/>
-    <sheet sheetId="16" name="student_health_report" state="visible" r:id="rId19"/>
-    <sheet sheetId="17" name="StudentDiary" state="visible" r:id="rId20"/>
-    <sheet sheetId="18" name="ParentNote" state="visible" r:id="rId21"/>
+    <sheet sheetId="14" name="feedback" state="hidden" r:id="rId17"/>
+    <sheet sheetId="15" name="StudentAttendanceLog" state="hidden" r:id="rId18"/>
+    <sheet sheetId="16" name="student_health_report" state="hidden" r:id="rId19"/>
+    <sheet sheetId="17" name="StudentDiary" state="hidden" r:id="rId20"/>
+    <sheet sheetId="18" name="ParentNote" state="hidden" r:id="rId21"/>
+    <sheet sheetId="19" name="StudentMarkSheet" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">coursetimetbl!$A$1:$J$79</definedName>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3492" uniqueCount="1824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3514" uniqueCount="1833">
   <si>
     <t>id</t>
   </si>
@@ -5508,6 +5509,33 @@
   </si>
   <si>
     <t>2026-09-01T15:30:43.991Z</t>
+  </si>
+  <si>
+    <t>ExamName</t>
+  </si>
+  <si>
+    <t>ExamDate</t>
+  </si>
+  <si>
+    <t>SubjTeacher</t>
+  </si>
+  <si>
+    <t>MaxMarks</t>
+  </si>
+  <si>
+    <t>MarksObtained</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>RecordedBy</t>
+  </si>
+  <si>
+    <t>45a3e33e-73ee-4fff-998d-a4812665ae4f</t>
+  </si>
+  <si>
+    <t>2026-09-01T16:17:48.479Z</t>
   </si>
 </sst>
 </file>
@@ -5631,19 +5659,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <family val="2"/>
       <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -5653,7 +5680,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C2185B"/>
+        <fgColor rgb="FFC2185B"/>
       </patternFill>
     </fill>
   </fills>
@@ -5667,16 +5694,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </left>
       <right style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </right>
       <top style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </top>
       <bottom style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="FFDDDDDD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -5686,58 +5713,58 @@
   </cellStyleXfs>
   <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="15" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7245,9 +7272,6 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <cols>
@@ -16482,9 +16506,6 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <cols>
@@ -16664,9 +16685,6 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <cols>
@@ -17122,9 +17140,6 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <cols>
@@ -17231,11 +17246,8 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -17326,6 +17338,96 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1825</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1827</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1828</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1829</v>
+      </c>
+      <c r="J1" t="s">
+        <v>370</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="L1" t="s">
+        <v>400</v>
+      </c>
+      <c r="M1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>60</v>
+      </c>
+      <c r="I2" t="s">
+        <v>195</v>
+      </c>
+      <c r="K2" t="s">
+        <v>298</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
@@ -17920,9 +18022,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <sheetData>
@@ -17962,9 +18061,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <cols>
@@ -18682,9 +18778,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <cols>
@@ -19083,9 +19176,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125"/>
   <cols>
